--- a/artfynd/A 44217-2025 artfynd.xlsx
+++ b/artfynd/A 44217-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129148420</v>
       </c>
       <c r="B2" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129148838</v>
       </c>
       <c r="B3" t="n">
-        <v>97528</v>
+        <v>97533</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,32 +894,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129148390</v>
+        <v>129147726</v>
       </c>
       <c r="B4" t="n">
-        <v>98651</v>
+        <v>57883</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,13 +929,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>538760</v>
+        <v>538679</v>
       </c>
       <c r="R4" t="n">
-        <v>6982387</v>
+        <v>6982379</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,32 +1001,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129147726</v>
+        <v>129148390</v>
       </c>
       <c r="B5" t="n">
-        <v>57883</v>
+        <v>98656</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,13 +1036,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>538679</v>
+        <v>538760</v>
       </c>
       <c r="R5" t="n">
-        <v>6982379</v>
+        <v>6982387</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,7 +1111,7 @@
         <v>129148489</v>
       </c>
       <c r="B6" t="n">
-        <v>105714</v>
+        <v>105719</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>129148326</v>
       </c>
       <c r="B8" t="n">
-        <v>97528</v>
+        <v>97533</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>129148311</v>
       </c>
       <c r="B9" t="n">
-        <v>97528</v>
+        <v>97533</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>129148383</v>
       </c>
       <c r="B10" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 44217-2025 artfynd.xlsx
+++ b/artfynd/A 44217-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129148420</v>
       </c>
       <c r="B2" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129148838</v>
       </c>
       <c r="B3" t="n">
-        <v>97533</v>
+        <v>97536</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>129148390</v>
       </c>
       <c r="B5" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>129148489</v>
       </c>
       <c r="B6" t="n">
-        <v>105719</v>
+        <v>105722</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>129149325</v>
       </c>
       <c r="B7" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>129148326</v>
       </c>
       <c r="B8" t="n">
-        <v>97533</v>
+        <v>97536</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>129148311</v>
       </c>
       <c r="B9" t="n">
-        <v>97533</v>
+        <v>97536</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>129148383</v>
       </c>
       <c r="B10" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 44217-2025 artfynd.xlsx
+++ b/artfynd/A 44217-2025 artfynd.xlsx
@@ -675,45 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129148420</v>
+        <v>129148838</v>
       </c>
       <c r="B2" t="n">
-        <v>98659</v>
+        <v>97546</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>538765</v>
+        <v>538554</v>
       </c>
       <c r="R2" t="n">
-        <v>6982359</v>
+        <v>6982305</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -745,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +759,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,6 +768,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -782,49 +787,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129148838</v>
+        <v>129148420</v>
       </c>
       <c r="B3" t="n">
-        <v>97536</v>
+        <v>98669</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>538554</v>
+        <v>538765</v>
       </c>
       <c r="R3" t="n">
-        <v>6982305</v>
+        <v>6982359</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -856,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -866,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -875,7 +876,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -897,7 +897,7 @@
         <v>129147726</v>
       </c>
       <c r="B4" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>129148390</v>
       </c>
       <c r="B5" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>129148489</v>
       </c>
       <c r="B6" t="n">
-        <v>105722</v>
+        <v>105732</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>129149325</v>
       </c>
       <c r="B7" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>129148326</v>
       </c>
       <c r="B8" t="n">
-        <v>97536</v>
+        <v>97546</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>129148311</v>
       </c>
       <c r="B9" t="n">
-        <v>97536</v>
+        <v>97546</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>129148383</v>
       </c>
       <c r="B10" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 44217-2025 artfynd.xlsx
+++ b/artfynd/A 44217-2025 artfynd.xlsx
@@ -675,49 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129148838</v>
+        <v>129148420</v>
       </c>
       <c r="B2" t="n">
-        <v>97546</v>
+        <v>98676</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>538554</v>
+        <v>538765</v>
       </c>
       <c r="R2" t="n">
-        <v>6982305</v>
+        <v>6982359</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -749,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -759,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -768,7 +764,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -787,45 +782,49 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129148420</v>
+        <v>129148838</v>
       </c>
       <c r="B3" t="n">
-        <v>98669</v>
+        <v>97553</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>538765</v>
+        <v>538554</v>
       </c>
       <c r="R3" t="n">
-        <v>6982359</v>
+        <v>6982305</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -857,7 +856,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +866,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -876,6 +875,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -1004,7 +1004,7 @@
         <v>129148390</v>
       </c>
       <c r="B5" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>129148489</v>
       </c>
       <c r="B6" t="n">
-        <v>105732</v>
+        <v>105739</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>129148326</v>
       </c>
       <c r="B8" t="n">
-        <v>97546</v>
+        <v>97553</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>129148311</v>
       </c>
       <c r="B9" t="n">
-        <v>97546</v>
+        <v>97553</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>129148383</v>
       </c>
       <c r="B10" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 44217-2025 artfynd.xlsx
+++ b/artfynd/A 44217-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129148420</v>
       </c>
       <c r="B2" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129148838</v>
       </c>
       <c r="B3" t="n">
-        <v>97553</v>
+        <v>97555</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,32 +894,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129147726</v>
+        <v>129148390</v>
       </c>
       <c r="B4" t="n">
-        <v>57885</v>
+        <v>98678</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,13 +929,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>538679</v>
+        <v>538760</v>
       </c>
       <c r="R4" t="n">
-        <v>6982379</v>
+        <v>6982387</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,32 +1001,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129148390</v>
+        <v>129147726</v>
       </c>
       <c r="B5" t="n">
-        <v>98676</v>
+        <v>57887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,13 +1036,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>538760</v>
+        <v>538679</v>
       </c>
       <c r="R5" t="n">
-        <v>6982387</v>
+        <v>6982379</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,7 +1111,7 @@
         <v>129148489</v>
       </c>
       <c r="B6" t="n">
-        <v>105739</v>
+        <v>105741</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>129149325</v>
       </c>
       <c r="B7" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>129148326</v>
       </c>
       <c r="B8" t="n">
-        <v>97553</v>
+        <v>97555</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>129148311</v>
       </c>
       <c r="B9" t="n">
-        <v>97553</v>
+        <v>97555</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>129148383</v>
       </c>
       <c r="B10" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 44217-2025 artfynd.xlsx
+++ b/artfynd/A 44217-2025 artfynd.xlsx
@@ -675,45 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129148420</v>
+        <v>129148838</v>
       </c>
       <c r="B2" t="n">
-        <v>98678</v>
+        <v>97555</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>538765</v>
+        <v>538554</v>
       </c>
       <c r="R2" t="n">
-        <v>6982359</v>
+        <v>6982305</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -745,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +759,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,6 +768,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -782,49 +787,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129148838</v>
+        <v>129148420</v>
       </c>
       <c r="B3" t="n">
-        <v>97555</v>
+        <v>98678</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>538554</v>
+        <v>538765</v>
       </c>
       <c r="R3" t="n">
-        <v>6982305</v>
+        <v>6982359</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -856,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -866,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -875,7 +876,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -894,32 +894,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129148390</v>
+        <v>129147726</v>
       </c>
       <c r="B4" t="n">
-        <v>98678</v>
+        <v>57887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,13 +929,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>538760</v>
+        <v>538679</v>
       </c>
       <c r="R4" t="n">
-        <v>6982387</v>
+        <v>6982379</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,32 +1001,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129147726</v>
+        <v>129148390</v>
       </c>
       <c r="B5" t="n">
-        <v>57887</v>
+        <v>98678</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,13 +1036,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>538679</v>
+        <v>538760</v>
       </c>
       <c r="R5" t="n">
-        <v>6982379</v>
+        <v>6982387</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 44217-2025 artfynd.xlsx
+++ b/artfynd/A 44217-2025 artfynd.xlsx
@@ -675,49 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129148838</v>
+        <v>129148420</v>
       </c>
       <c r="B2" t="n">
-        <v>97555</v>
+        <v>98704</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>538554</v>
+        <v>538765</v>
       </c>
       <c r="R2" t="n">
-        <v>6982305</v>
+        <v>6982359</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -749,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -759,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -768,7 +764,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -787,45 +782,49 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129148420</v>
+        <v>129148838</v>
       </c>
       <c r="B3" t="n">
-        <v>98678</v>
+        <v>97581</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>538765</v>
+        <v>538554</v>
       </c>
       <c r="R3" t="n">
-        <v>6982359</v>
+        <v>6982305</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -857,7 +856,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +866,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -876,6 +875,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -1004,7 +1004,7 @@
         <v>129148390</v>
       </c>
       <c r="B5" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>129148489</v>
       </c>
       <c r="B6" t="n">
-        <v>105741</v>
+        <v>105767</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>129148326</v>
       </c>
       <c r="B8" t="n">
-        <v>97555</v>
+        <v>97581</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>129148311</v>
       </c>
       <c r="B9" t="n">
-        <v>97555</v>
+        <v>97581</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>129148383</v>
       </c>
       <c r="B10" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 44217-2025 artfynd.xlsx
+++ b/artfynd/A 44217-2025 artfynd.xlsx
@@ -675,45 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129148420</v>
+        <v>129148838</v>
       </c>
       <c r="B2" t="n">
-        <v>98704</v>
+        <v>97582</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>538765</v>
+        <v>538554</v>
       </c>
       <c r="R2" t="n">
-        <v>6982359</v>
+        <v>6982305</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -745,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +759,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,6 +768,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -782,49 +787,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129148838</v>
+        <v>129148420</v>
       </c>
       <c r="B3" t="n">
-        <v>97581</v>
+        <v>98705</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>538554</v>
+        <v>538765</v>
       </c>
       <c r="R3" t="n">
-        <v>6982305</v>
+        <v>6982359</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -856,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -866,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -875,7 +876,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -1004,7 +1004,7 @@
         <v>129148390</v>
       </c>
       <c r="B5" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>129148489</v>
       </c>
       <c r="B6" t="n">
-        <v>105767</v>
+        <v>105769</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>129148326</v>
       </c>
       <c r="B8" t="n">
-        <v>97581</v>
+        <v>97582</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>129148311</v>
       </c>
       <c r="B9" t="n">
-        <v>97581</v>
+        <v>97582</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>129148383</v>
       </c>
       <c r="B10" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 44217-2025 artfynd.xlsx
+++ b/artfynd/A 44217-2025 artfynd.xlsx
@@ -675,49 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129148838</v>
+        <v>129148420</v>
       </c>
       <c r="B2" t="n">
-        <v>97582</v>
+        <v>98706</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>538554</v>
+        <v>538765</v>
       </c>
       <c r="R2" t="n">
-        <v>6982305</v>
+        <v>6982359</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -749,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -759,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -768,7 +764,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -787,45 +782,49 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129148420</v>
+        <v>129148838</v>
       </c>
       <c r="B3" t="n">
-        <v>98705</v>
+        <v>97583</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>538765</v>
+        <v>538554</v>
       </c>
       <c r="R3" t="n">
-        <v>6982359</v>
+        <v>6982305</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -857,7 +856,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +866,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -876,6 +875,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -1004,7 +1004,7 @@
         <v>129148390</v>
       </c>
       <c r="B5" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>129148489</v>
       </c>
       <c r="B6" t="n">
-        <v>105769</v>
+        <v>105770</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>129148326</v>
       </c>
       <c r="B8" t="n">
-        <v>97582</v>
+        <v>97583</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>129148311</v>
       </c>
       <c r="B9" t="n">
-        <v>97582</v>
+        <v>97583</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>129148383</v>
       </c>
       <c r="B10" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 44217-2025 artfynd.xlsx
+++ b/artfynd/A 44217-2025 artfynd.xlsx
@@ -675,45 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129148420</v>
+        <v>129148838</v>
       </c>
       <c r="B2" t="n">
-        <v>98706</v>
+        <v>97587</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>538765</v>
+        <v>538554</v>
       </c>
       <c r="R2" t="n">
-        <v>6982359</v>
+        <v>6982305</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -745,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +759,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,6 +768,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -782,49 +787,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129148838</v>
+        <v>129148420</v>
       </c>
       <c r="B3" t="n">
-        <v>97583</v>
+        <v>98710</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>538554</v>
+        <v>538765</v>
       </c>
       <c r="R3" t="n">
-        <v>6982305</v>
+        <v>6982359</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -856,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -866,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -875,7 +876,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -1004,7 +1004,7 @@
         <v>129148390</v>
       </c>
       <c r="B5" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>129148489</v>
       </c>
       <c r="B6" t="n">
-        <v>105770</v>
+        <v>105774</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>129149325</v>
       </c>
       <c r="B7" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>129148326</v>
       </c>
       <c r="B8" t="n">
-        <v>97583</v>
+        <v>97587</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>129148311</v>
       </c>
       <c r="B9" t="n">
-        <v>97583</v>
+        <v>97587</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>129148383</v>
       </c>
       <c r="B10" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 44217-2025 artfynd.xlsx
+++ b/artfynd/A 44217-2025 artfynd.xlsx
@@ -675,49 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129148838</v>
+        <v>129148420</v>
       </c>
       <c r="B2" t="n">
-        <v>97587</v>
+        <v>98712</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>538554</v>
+        <v>538765</v>
       </c>
       <c r="R2" t="n">
-        <v>6982305</v>
+        <v>6982359</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -749,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -759,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -768,7 +764,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -787,45 +782,49 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129148420</v>
+        <v>129148838</v>
       </c>
       <c r="B3" t="n">
-        <v>98710</v>
+        <v>97589</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>538765</v>
+        <v>538554</v>
       </c>
       <c r="R3" t="n">
-        <v>6982359</v>
+        <v>6982305</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -857,7 +856,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +866,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -876,6 +875,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -1004,7 +1004,7 @@
         <v>129148390</v>
       </c>
       <c r="B5" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>129148489</v>
       </c>
       <c r="B6" t="n">
-        <v>105774</v>
+        <v>105776</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>129149325</v>
       </c>
       <c r="B7" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>129148326</v>
       </c>
       <c r="B8" t="n">
-        <v>97587</v>
+        <v>97589</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>129148311</v>
       </c>
       <c r="B9" t="n">
-        <v>97587</v>
+        <v>97589</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>129148383</v>
       </c>
       <c r="B10" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 44217-2025 artfynd.xlsx
+++ b/artfynd/A 44217-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129148420</v>
       </c>
       <c r="B2" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129148838</v>
       </c>
       <c r="B3" t="n">
-        <v>97589</v>
+        <v>97593</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,32 +894,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129147726</v>
+        <v>129148390</v>
       </c>
       <c r="B4" t="n">
-        <v>57887</v>
+        <v>98716</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,13 +929,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>538679</v>
+        <v>538760</v>
       </c>
       <c r="R4" t="n">
-        <v>6982379</v>
+        <v>6982387</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,32 +1001,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129148390</v>
+        <v>129147726</v>
       </c>
       <c r="B5" t="n">
-        <v>98712</v>
+        <v>57887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,13 +1036,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>538760</v>
+        <v>538679</v>
       </c>
       <c r="R5" t="n">
-        <v>6982387</v>
+        <v>6982379</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,7 +1111,7 @@
         <v>129148489</v>
       </c>
       <c r="B6" t="n">
-        <v>105776</v>
+        <v>105780</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>129148326</v>
       </c>
       <c r="B8" t="n">
-        <v>97589</v>
+        <v>97593</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>129148311</v>
       </c>
       <c r="B9" t="n">
-        <v>97589</v>
+        <v>97593</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>129148383</v>
       </c>
       <c r="B10" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 44217-2025 artfynd.xlsx
+++ b/artfynd/A 44217-2025 artfynd.xlsx
@@ -675,45 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129148420</v>
+        <v>129148838</v>
       </c>
       <c r="B2" t="n">
-        <v>98716</v>
+        <v>97601</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>538765</v>
+        <v>538554</v>
       </c>
       <c r="R2" t="n">
-        <v>6982359</v>
+        <v>6982305</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -745,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +759,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,6 +768,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -782,49 +787,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129148838</v>
+        <v>129148420</v>
       </c>
       <c r="B3" t="n">
-        <v>97593</v>
+        <v>98724</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>538554</v>
+        <v>538765</v>
       </c>
       <c r="R3" t="n">
-        <v>6982305</v>
+        <v>6982359</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -856,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -866,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -875,7 +876,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -894,32 +894,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129148390</v>
+        <v>129147726</v>
       </c>
       <c r="B4" t="n">
-        <v>98716</v>
+        <v>57887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,13 +929,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>538760</v>
+        <v>538679</v>
       </c>
       <c r="R4" t="n">
-        <v>6982387</v>
+        <v>6982379</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,32 +1001,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129147726</v>
+        <v>129148390</v>
       </c>
       <c r="B5" t="n">
-        <v>57887</v>
+        <v>98724</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,13 +1036,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>538679</v>
+        <v>538760</v>
       </c>
       <c r="R5" t="n">
-        <v>6982379</v>
+        <v>6982387</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,7 +1111,7 @@
         <v>129148489</v>
       </c>
       <c r="B6" t="n">
-        <v>105780</v>
+        <v>105790</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>129148326</v>
       </c>
       <c r="B8" t="n">
-        <v>97593</v>
+        <v>97601</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>129148311</v>
       </c>
       <c r="B9" t="n">
-        <v>97593</v>
+        <v>97601</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>129148383</v>
       </c>
       <c r="B10" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 44217-2025 artfynd.xlsx
+++ b/artfynd/A 44217-2025 artfynd.xlsx
@@ -675,49 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129148838</v>
+        <v>129148420</v>
       </c>
       <c r="B2" t="n">
-        <v>97601</v>
+        <v>98724</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>538554</v>
+        <v>538765</v>
       </c>
       <c r="R2" t="n">
-        <v>6982305</v>
+        <v>6982359</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -749,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -759,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -768,7 +764,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -787,45 +782,49 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129148420</v>
+        <v>129148838</v>
       </c>
       <c r="B3" t="n">
-        <v>98724</v>
+        <v>97601</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>538765</v>
+        <v>538554</v>
       </c>
       <c r="R3" t="n">
-        <v>6982359</v>
+        <v>6982305</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -857,7 +856,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +866,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -876,6 +875,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 44217-2025 artfynd.xlsx
+++ b/artfynd/A 44217-2025 artfynd.xlsx
@@ -675,45 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129148420</v>
+        <v>129148838</v>
       </c>
       <c r="B2" t="n">
-        <v>98724</v>
+        <v>97604</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>538765</v>
+        <v>538554</v>
       </c>
       <c r="R2" t="n">
-        <v>6982359</v>
+        <v>6982305</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -745,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +759,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,6 +768,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -782,49 +787,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129148838</v>
+        <v>129148420</v>
       </c>
       <c r="B3" t="n">
-        <v>97601</v>
+        <v>98727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>538554</v>
+        <v>538765</v>
       </c>
       <c r="R3" t="n">
-        <v>6982305</v>
+        <v>6982359</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -856,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -866,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -875,7 +876,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -1004,7 +1004,7 @@
         <v>129148390</v>
       </c>
       <c r="B5" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>129148489</v>
       </c>
       <c r="B6" t="n">
-        <v>105790</v>
+        <v>105793</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>129148326</v>
       </c>
       <c r="B8" t="n">
-        <v>97601</v>
+        <v>97604</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>129148311</v>
       </c>
       <c r="B9" t="n">
-        <v>97601</v>
+        <v>97604</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>129148383</v>
       </c>
       <c r="B10" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 44217-2025 artfynd.xlsx
+++ b/artfynd/A 44217-2025 artfynd.xlsx
@@ -894,32 +894,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129147726</v>
+        <v>129148390</v>
       </c>
       <c r="B4" t="n">
-        <v>57887</v>
+        <v>98727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,13 +929,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>538679</v>
+        <v>538760</v>
       </c>
       <c r="R4" t="n">
-        <v>6982379</v>
+        <v>6982387</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,32 +1001,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129148390</v>
+        <v>129147726</v>
       </c>
       <c r="B5" t="n">
-        <v>98727</v>
+        <v>57887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,13 +1036,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>538760</v>
+        <v>538679</v>
       </c>
       <c r="R5" t="n">
-        <v>6982387</v>
+        <v>6982379</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 44217-2025 artfynd.xlsx
+++ b/artfynd/A 44217-2025 artfynd.xlsx
@@ -894,32 +894,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129148390</v>
+        <v>129147726</v>
       </c>
       <c r="B4" t="n">
-        <v>98727</v>
+        <v>57887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,13 +929,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>538760</v>
+        <v>538679</v>
       </c>
       <c r="R4" t="n">
-        <v>6982387</v>
+        <v>6982379</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,32 +1001,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129147726</v>
+        <v>129148390</v>
       </c>
       <c r="B5" t="n">
-        <v>57887</v>
+        <v>98727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,13 +1036,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>538679</v>
+        <v>538760</v>
       </c>
       <c r="R5" t="n">
-        <v>6982379</v>
+        <v>6982387</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 44217-2025 artfynd.xlsx
+++ b/artfynd/A 44217-2025 artfynd.xlsx
@@ -675,49 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129148838</v>
+        <v>129148420</v>
       </c>
       <c r="B2" t="n">
-        <v>97604</v>
+        <v>98727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>538554</v>
+        <v>538765</v>
       </c>
       <c r="R2" t="n">
-        <v>6982305</v>
+        <v>6982359</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -749,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -759,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -768,7 +764,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -787,45 +782,49 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129148420</v>
+        <v>129148838</v>
       </c>
       <c r="B3" t="n">
-        <v>98727</v>
+        <v>97604</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>538765</v>
+        <v>538554</v>
       </c>
       <c r="R3" t="n">
-        <v>6982359</v>
+        <v>6982305</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -857,7 +856,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +866,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -876,6 +875,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 44217-2025 artfynd.xlsx
+++ b/artfynd/A 44217-2025 artfynd.xlsx
@@ -675,45 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129148420</v>
+        <v>129148838</v>
       </c>
       <c r="B2" t="n">
-        <v>98727</v>
+        <v>97604</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>538765</v>
+        <v>538554</v>
       </c>
       <c r="R2" t="n">
-        <v>6982359</v>
+        <v>6982305</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -745,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +759,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,6 +768,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -782,49 +787,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129148838</v>
+        <v>129148420</v>
       </c>
       <c r="B3" t="n">
-        <v>97604</v>
+        <v>98727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>538554</v>
+        <v>538765</v>
       </c>
       <c r="R3" t="n">
-        <v>6982305</v>
+        <v>6982359</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -856,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -866,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -875,7 +876,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 44217-2025 artfynd.xlsx
+++ b/artfynd/A 44217-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129148838</v>
       </c>
       <c r="B2" t="n">
-        <v>97604</v>
+        <v>97633</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>129148420</v>
       </c>
       <c r="B3" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>129147726</v>
       </c>
       <c r="B4" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>129148390</v>
       </c>
       <c r="B5" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>129148489</v>
       </c>
       <c r="B6" t="n">
-        <v>105793</v>
+        <v>105822</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>129149325</v>
       </c>
       <c r="B7" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>129148326</v>
       </c>
       <c r="B8" t="n">
-        <v>97604</v>
+        <v>97633</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>129148311</v>
       </c>
       <c r="B9" t="n">
-        <v>97604</v>
+        <v>97633</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>129148383</v>
       </c>
       <c r="B10" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 44217-2025 artfynd.xlsx
+++ b/artfynd/A 44217-2025 artfynd.xlsx
@@ -894,32 +894,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129147726</v>
+        <v>129148390</v>
       </c>
       <c r="B4" t="n">
-        <v>57890</v>
+        <v>98756</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,13 +929,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>538679</v>
+        <v>538760</v>
       </c>
       <c r="R4" t="n">
-        <v>6982379</v>
+        <v>6982387</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,32 +1001,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129148390</v>
+        <v>129147726</v>
       </c>
       <c r="B5" t="n">
-        <v>98756</v>
+        <v>57890</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,13 +1036,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>538760</v>
+        <v>538679</v>
       </c>
       <c r="R5" t="n">
-        <v>6982387</v>
+        <v>6982379</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 44217-2025 artfynd.xlsx
+++ b/artfynd/A 44217-2025 artfynd.xlsx
@@ -766,7 +766,7 @@
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
@@ -1199,7 +1199,7 @@
         <v>0</v>
       </c>
       <c r="AE6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
@@ -1414,7 +1414,7 @@
         <v>0</v>
       </c>
       <c r="AE8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG8" t="b">
         <v>0</v>
@@ -1521,7 +1521,7 @@
         <v>0</v>
       </c>
       <c r="AE9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG9" t="b">
         <v>0</v>
